--- a/Resource/素材/バグ（本命）.xlsx
+++ b/Resource/素材/バグ（本命）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K245018\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k245020\Documents\就職作品\Team\Resource\素材\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE4D843-D704-41AE-B454-C8B78BA836AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A6E0FA-D065-4A64-AFB9-6016909578F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{AB49FEB1-EFEA-464B-B015-9280E7DC8C55}"/>
+    <workbookView xWindow="216" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{AB49FEB1-EFEA-464B-B015-9280E7DC8C55}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,10 +84,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　　　　</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <t>・</t>
     </r>
@@ -130,10 +126,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　　　　　</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・必殺技を使う時に雑魚敵から攻撃をくらうと必殺技のモーションが消えて必殺ゲージも消える</t>
     <rPh sb="1" eb="4">
       <t>ヒッサツワザ</t>
@@ -180,6 +172,14 @@
     <rPh sb="17" eb="18">
       <t>タオ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　　〇</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -843,14 +843,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D23608-E206-4910-B63B-123A8997CC86}">
   <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="93.08203125" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.58203125" customWidth="1"/>
+    <col min="1" max="1" width="93.09765625" customWidth="1"/>
+    <col min="2" max="2" width="24.296875" customWidth="1"/>
+    <col min="3" max="3" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -876,12 +876,12 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18" ht="55.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -900,12 +900,12 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -924,12 +924,12 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="57.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="57.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>2</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -947,12 +947,12 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -971,9 +971,9 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="1"/>
@@ -993,9 +993,9 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="1"/>
@@ -1015,9 +1015,9 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="1"/>
@@ -1037,12 +1037,12 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="36.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1061,9 +1061,9 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18" ht="49.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="1"/>
@@ -1083,9 +1083,9 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="55" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18" ht="55.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="1"/>
@@ -1105,7 +1105,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1125,7 +1125,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1145,7 +1145,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1165,7 +1165,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1185,7 +1185,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1205,7 +1205,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1225,7 +1225,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1245,7 +1245,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1265,7 +1265,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1285,7 +1285,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1305,7 +1305,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1325,7 +1325,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>

--- a/Resource/素材/バグ（本命）.xlsx
+++ b/Resource/素材/バグ（本命）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K245018\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K245018\Documents\就職活動用作品\Team\Resource\素材\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE4D843-D704-41AE-B454-C8B78BA836AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC341241-220E-427D-95F2-06332876C78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{AB49FEB1-EFEA-464B-B015-9280E7DC8C55}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <r>
       <t>　</t>
@@ -179,6 +179,19 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・プレイヤーの行動するボタンを全て同時に押すと敵がフリーズするけどプレイヤーは動き回れる</t>
+    <rPh sb="23" eb="24">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>マワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -381,7 +394,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -407,9 +420,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
@@ -925,7 +935,7 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="57.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -947,9 +957,9 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="9" t="s">
-        <v>9</v>
+    <row r="5" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>6</v>
@@ -972,9 +982,7 @@
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="7"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -1016,7 +1024,7 @@
       <c r="R7" s="1"/>
     </row>
     <row r="8" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
@@ -1062,7 +1070,7 @@
       <c r="R9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="50" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="8"/>
@@ -1084,7 +1092,7 @@
       <c r="R10" s="1"/>
     </row>
     <row r="11" spans="1:18" ht="55" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="8"/>
